--- a/MainTop/29.04.2026 Таня ВБ/print_print_sorted.xlsx
+++ b/MainTop/29.04.2026 Таня ВБ/print_print_sorted.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I161"/>
+  <dimension ref="A1:I177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4055,14 +4055,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Сердце Бабочки летят</t>
+          <t>Термонаклейка Шредер и Кренг из Черепашек-ниндзя</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>12</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -4084,20 +4084,20 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>-28.9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Рука Фатимы</t>
+          <t>Термонаклейка Сердце Бабочки летят</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>0</v>
@@ -4119,20 +4119,20 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>-29.8</v>
+        <v>-28.9</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Карточная королева кричит</t>
+          <t>Термонаклейка Рука Фатимы</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>0</v>
@@ -4154,17 +4154,17 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>-23.4</v>
+        <v>-29.8</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Цветы Розовые Spring Blossoms</t>
+          <t>Термонаклейка Карточная королева кричит</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="C106" s="2" t="n">
         <v>14</v>
@@ -4189,20 +4189,20 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>-23.2</v>
+        <v>-23.4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Девушка силует обнимают природа</t>
+          <t>Термонаклейка Цветы Розовые Spring Blossoms</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>0</v>
@@ -4224,20 +4224,20 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>-16.8</v>
+        <v>-23.2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Сова в цветах</t>
+          <t>Термонаклейка Девушка силует обнимают природа</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>0</v>
@@ -4259,20 +4259,20 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>-14.7</v>
+        <v>-16.8</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Рука жест рок металл</t>
+          <t>Термонаклейка Сова в цветах</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>0</v>
@@ -4294,20 +4294,20 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>-15.9</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Кит в голубых и розовых оттенках</t>
+          <t>Термонаклейка Рука жест рок металл</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D110" s="2" t="n">
         <v>0</v>
@@ -4329,20 +4329,20 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>-18.9</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Микки Маус бабочки цверы силует</t>
+          <t>Термонаклейка Кит в голубых и розовых оттенках</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>0</v>
@@ -4364,13 +4364,13 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>-14.8</v>
+        <v>-18.9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Змеи черная белая 2шт</t>
+          <t>Термонаклейка Микки Маус бабочки цверы силует</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -4405,14 +4405,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Графичное лицо в чёрно-белом</t>
+          <t>Термонаклейка Змеи черная белая 2шт</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>0</v>
@@ -4434,20 +4434,20 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>-13.5</v>
+        <v>-14.8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Леопард пятна сердечки полностью</t>
+          <t>Термонаклейка Графичное лицо в чёрно-белом</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>0</v>
@@ -4469,20 +4469,20 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>-11.3</v>
+        <v>-13.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Одри Хепбёрн холст Vogue</t>
+          <t>Термонаклейка Леопард пятна сердечки полностью</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>0</v>
@@ -4504,20 +4504,20 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>-17.9</v>
+        <v>-11.3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Чёрный кот Catzilla Годзилла луч</t>
+          <t>Термонаклейка Одри Хепбёрн холст Vogue</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>0</v>
@@ -4539,20 +4539,20 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>-14.8</v>
+        <v>-17.9</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Девушка в поле розовых цветов</t>
+          <t>Термонаклейка Чёрный кот Catzilla Годзилла луч</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>0</v>
@@ -4574,20 +4574,20 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>-13.6</v>
+        <v>-14.8</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Мэрилин Монро Медуза Горгона</t>
+          <t>Термонаклейка Девушка в поле розовых цветов</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>0</v>
@@ -4609,20 +4609,20 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>-12.4</v>
+        <v>-13.6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Ветви с белыми цветами</t>
+          <t>Термонаклейка Мэрилин Монро Медуза Горгона</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>0</v>
@@ -4644,20 +4644,20 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>-10.1</v>
+        <v>-12.4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Фламинго трое на воде право</t>
+          <t>Термонаклейка Ветви с белыми цветами</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>0</v>
@@ -4679,20 +4679,20 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>-9</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Летающий кит и город</t>
+          <t>Термонаклейка Фламинго трое на воде право</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>0</v>
@@ -4714,17 +4714,17 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Мопс Собачка попа секси</t>
+          <t>Термонаклейка Акира Глаз ядерный взрыв</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C122" s="2" t="n">
         <v>1</v>
@@ -4749,20 +4749,20 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>-9.1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Адам и Ева яблоко змея</t>
+          <t>Термонаклейка Летающий кит и город</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>0</v>
@@ -4784,20 +4784,20 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>-10.1</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Девушка в маках сон</t>
+          <t>Термонаклейка Мопс Собачка попа секси</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>0</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>-12</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Астронавт и часы</t>
+          <t>Термонаклейка Адам и Ева яблоко змея</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
@@ -4860,14 +4860,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Девушка яркий арт стиль</t>
+          <t>Термонаклейка Девушка в маках сон</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>0</v>
@@ -4889,20 +4889,20 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Акира и мотоцикл Аниме</t>
+          <t>Термонаклейка Астронавт и часы</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>0</v>
@@ -4924,17 +4924,17 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>-8.1</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Сердце в руках арт</t>
+          <t>Термонаклейка Девушка яркий арт стиль</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C128" s="2" t="n">
         <v>3</v>
@@ -4959,20 +4959,20 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>-11.1</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Заяц неон арт персонаж</t>
+          <t>Термонаклейка Акира и мотоцикл Аниме</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>0</v>
@@ -4994,20 +4994,20 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>-10.1</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Человек Паук Лого позади</t>
+          <t>Термонаклейка Акира на троне среди металлолома</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0</v>
@@ -5016,11 +5016,11 @@
         <v>12</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -5029,20 +5029,20 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>32.3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Зайка балерина</t>
+          <t>Термонаклейка Сердце в руках арт</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>4.6</v>
+        <v>0.1</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>0</v>
@@ -5051,11 +5051,11 @@
         <v>12</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -5064,20 +5064,20 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>-11.6</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Зайчик ромашка в руках</t>
+          <t>Термонаклейка Заяц неон арт персонаж</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>0</v>
@@ -5086,11 +5086,11 @@
         <v>12</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -5099,20 +5099,20 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>12.1</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Лило и Стич сидят</t>
+          <t>Термонаклейка Шрек мем поднимает голову</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>0</v>
@@ -5121,11 +5121,11 @@
         <v>12</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -5134,20 +5134,20 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>-2.899999999999999</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Дисней утка Дейзи и Минни пис</t>
+          <t>Термонаклейка Кибер-девушка в стиле аниме</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>0</v>
@@ -5156,11 +5156,11 @@
         <v>12</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -5169,20 +5169,20 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Весёлый енот выглядывает</t>
+          <t>Термонаклейка Череп с рогами и логотипом Metallica</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>0</v>
@@ -5191,11 +5191,11 @@
         <v>12</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -5204,20 +5204,20 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>-24.8</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Разноцветные сердечки</t>
+          <t>Термонаклейка Берсерк воин в аниме стиле</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>0</v>
@@ -5226,11 +5226,11 @@
         <v>12</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -5239,20 +5239,20 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>-17.8</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Миньон с бананами</t>
+          <t>Термонаклейка Акира мотоцикл и разрушения</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>0</v>
@@ -5261,11 +5261,11 @@
         <v>12</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -5274,20 +5274,20 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>3.199999999999999</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Термонаклейка Котята на качелях</t>
+          <t>Термонаклейка Киберпанк череп с ирокезом</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D138" s="2" t="n">
         <v>0</v>
@@ -5296,313 +5296,313 @@
         <v>12</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
+          <t>1_а4</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Термонаклейка Кибердевушка с капюшоном</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>1_а4</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Термонаклейка Яркие коты неон арт</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>1_а4</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Термонаклейка Человек Паук Лого позади</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
           <t>2_а5</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>-17.1</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>Термонаклейка Марвел супергерои 4 верт фона</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C139" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="D139" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F139" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G139" s="3" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Термонаклейка Зайка балерина</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>2_а5</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I139" s="3" t="n">
-        <v>-20.2</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>Термонаклейка Ёжики в кружках с сердечками</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C140" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D140" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F140" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G140" s="3" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>-11.6</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Термонаклейка Зайчик ромашка в руках</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>2_а5</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I140" s="3" t="n">
-        <v>-1.800000000000001</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>Термонаклейка Девочка в розовом платье</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C141" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D141" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F141" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G141" s="3" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Термонаклейка Лило и Стич сидят</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>2_а5</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I141" s="3" t="n">
-        <v>-20.9</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>Термонаклейка Сова розовая</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C142" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="D142" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F142" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G142" s="3" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>-2.899999999999999</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Термонаклейка Дисней утка Дейзи и Минни пис</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>2_а5</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I142" s="3" t="n">
-        <v>-18.5</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>Термонаклейка Спанч Боб и друзья Keep Vibes</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C143" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D143" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F143" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G143" s="3" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Термонаклейка Весёлый енот выглядывает</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>2_а5</t>
         </is>
       </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I143" s="3" t="n">
-        <v>-13.1</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>Термонаклейка Три Миньона бегут</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C144" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F144" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G144" s="3" t="inlineStr">
-        <is>
-          <t>2_а5</t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I144" s="3" t="n">
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>Термонаклейка Минни Маус целует Микки</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C145" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D145" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F145" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G145" s="3" t="inlineStr">
-        <is>
-          <t>2_а5</t>
-        </is>
-      </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I145" s="3" t="n">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>Термонаклейка Лисёнок в свитере с узорами</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C146" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F146" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G146" s="3" t="inlineStr">
-        <is>
-          <t>2_а5</t>
-        </is>
-      </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I146" s="3" t="n">
-        <v>-4.6</v>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>-24.8</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>Термонаклейка Человек Паук Лого круг</t>
+          <t>Термонаклейка Разноцветные сердечки</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="C147" s="3" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
         <v>12</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -5624,20 +5624,20 @@
         </is>
       </c>
       <c r="I147" s="3" t="n">
-        <v>-5.6</v>
+        <v>-17.8</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>Термонаклейка Звезды Белые термозаплатка</t>
+          <t>Термонаклейка Миньон с бананами</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C148" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D148" s="3" t="n">
         <v>0</v>
@@ -5646,7 +5646,7 @@
         <v>12</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
@@ -5659,20 +5659,20 @@
         </is>
       </c>
       <c r="I148" s="3" t="n">
-        <v>-8.699999999999999</v>
+        <v>3.199999999999999</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>Термонаклейка Собачка в очках язык</t>
+          <t>Термонаклейка Котята на качелях</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="C149" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>0</v>
@@ -5681,7 +5681,7 @@
         <v>12</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -5694,20 +5694,20 @@
         </is>
       </c>
       <c r="I149" s="3" t="n">
-        <v>-5.6</v>
+        <v>-17.1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>Термонаклейка Котенок с цветами ромашками</t>
+          <t>Термонаклейка Марвел супергерои 4 верт фона</t>
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="C150" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D150" s="3" t="n">
         <v>0</v>
@@ -5716,7 +5716,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
@@ -5735,14 +5735,14 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>Термонаклейка Дисней утка Дейзи и Минни сидят</t>
+          <t>Термонаклейка Ёжики в кружках с сердечками</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C151" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>0</v>
@@ -5751,7 +5751,7 @@
         <v>12</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -5764,20 +5764,20 @@
         </is>
       </c>
       <c r="I151" s="3" t="n">
-        <v>-14.7</v>
+        <v>-1.800000000000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>Термонаклейка Человек Паук синий белый круг</t>
+          <t>Термонаклейка Девочка в розовом платье</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="C152" s="3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D152" s="3" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
         <v>12</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
@@ -5799,20 +5799,20 @@
         </is>
       </c>
       <c r="I152" s="3" t="n">
-        <v>-14.7</v>
+        <v>-20.9</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>Термонаклейка Барт с рогаткой Симпсоны</t>
+          <t>Термонаклейка Сова розовая</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="C153" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>12</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -5834,20 +5834,20 @@
         </is>
       </c>
       <c r="I153" s="3" t="n">
-        <v>-14.6</v>
+        <v>-18.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>Термонаклейка Соник Ежик бежит пис мир рука</t>
+          <t>Термонаклейка Спанч Боб и друзья Keep Vibes</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="C154" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D154" s="3" t="n">
         <v>0</v>
@@ -5856,7 +5856,7 @@
         <v>12</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
@@ -5869,21 +5869,21 @@
         </is>
       </c>
       <c r="I154" s="3" t="n">
-        <v>-17.8</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>Термонаклейка Акула серфинг в очках</t>
+          <t>Термонаклейка Три Миньона бегут</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C155" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C155" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="D155" s="3" t="n">
         <v>0</v>
       </c>
@@ -5891,7 +5891,7 @@
         <v>12</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -5904,20 +5904,20 @@
         </is>
       </c>
       <c r="I155" s="3" t="n">
-        <v>-20</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>Термонаклейка Единорог ресницы цветы уши</t>
+          <t>Термонаклейка Минни Маус целует Микки</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C156" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D156" s="3" t="n">
         <v>0</v>
@@ -5926,7 +5926,7 @@
         <v>12</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
@@ -5939,181 +5939,741 @@
         </is>
       </c>
       <c r="I156" s="3" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
+          <t>Термонаклейка Лисёнок в свитере с узорами</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v>-4.6</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Человек Паук Лого круг</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Звезды Белые термозаплатка</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Собачка в очках язык</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Котенок с цветами ромашками</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>-20.2</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Дисней утка Дейзи и Минни сидят</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="n">
+        <v>-14.7</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Человек Паук синий белый круг</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="n">
+        <v>-14.7</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Барт с рогаткой Симпсоны</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v>-14.6</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Соник Ежик бежит пис мир рука</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v>-17.8</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Акула серфинг в очках</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Единорог ресницы цветы уши</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
           <t>Термонаклейка Мишка Серфинг с парусом волна</t>
         </is>
       </c>
-      <c r="B157" s="3" t="n">
+      <c r="B168" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="C157" s="3" t="n">
+      <c r="C168" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D157" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F157" s="3" t="n">
+      <c r="D168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F168" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G157" s="3" t="inlineStr">
+      <c r="G168" s="3" t="inlineStr">
         <is>
           <t>2_а5</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I157" s="3" t="n">
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="n">
         <v>-9.1</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="7" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Мишка скейт бежит</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Мишка гидроцикл волна лето</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Мишка репер читает с микрофоном</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I171" s="3" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Мишка велосипед</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>Термонаклейка Мишка стоит с скейтом</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="inlineStr">
         <is>
           <t>Термонаклейка Кошка розово-фиолетовая крупный план</t>
         </is>
       </c>
-      <c r="B158" s="7" t="n">
+      <c r="B174" s="7" t="n">
         <v>1.7</v>
       </c>
-      <c r="C158" s="7" t="n">
+      <c r="C174" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="D158" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E158" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="F158" s="7" t="n">
+      <c r="D174" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F174" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="G158" s="7" t="inlineStr">
+      <c r="G174" s="7" t="inlineStr">
         <is>
           <t>6_а4_настройки_60</t>
         </is>
       </c>
-      <c r="H158" s="7" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I158" s="7" t="n">
+      <c r="H174" s="7" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I174" s="7" t="n">
         <v>-21.7</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="7" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
         <is>
           <t>Термонаклейка Кит в розовых облаках</t>
         </is>
       </c>
-      <c r="B159" s="7" t="n">
+      <c r="B175" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="C159" s="7" t="n">
+      <c r="C175" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D159" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E159" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="F159" s="7" t="n">
+      <c r="D175" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F175" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="G159" s="7" t="inlineStr">
+      <c r="G175" s="7" t="inlineStr">
         <is>
           <t>6_а4_настройки_60</t>
         </is>
       </c>
-      <c r="H159" s="7" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I159" s="7" t="n">
+      <c r="H175" s="7" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I175" s="7" t="n">
         <v>-6.1</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="7" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="7" t="inlineStr">
         <is>
           <t>Термонаклейка Девушка-кошка с чёрным котом поцелуй</t>
         </is>
       </c>
-      <c r="B160" s="7" t="n">
+      <c r="B176" s="7" t="n">
         <v>0.9</v>
       </c>
-      <c r="C160" s="7" t="n">
+      <c r="C176" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="D160" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E160" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="F160" s="7" t="n">
+      <c r="D176" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F176" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G160" s="7" t="inlineStr">
+      <c r="G176" s="7" t="inlineStr">
         <is>
           <t>6_а4_настройки_60</t>
         </is>
       </c>
-      <c r="H160" s="7" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I160" s="7" t="n">
+      <c r="H176" s="7" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I176" s="7" t="n">
         <v>-15.9</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="7" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr">
         <is>
           <t>Термонаклейка Пантера рычит звезды розовый фон</t>
         </is>
       </c>
-      <c r="B161" s="7" t="n">
+      <c r="B177" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="C161" s="7" t="n">
+      <c r="C177" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D161" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E161" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="F161" s="7" t="n">
+      <c r="D177" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F177" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G161" s="7" t="inlineStr">
+      <c r="G177" s="7" t="inlineStr">
         <is>
           <t>6_а4_настройки_60</t>
         </is>
       </c>
-      <c r="H161" s="7" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I161" s="7" t="n">
+      <c r="H177" s="7" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I177" s="7" t="n">
         <v>-13.6</v>
       </c>
     </row>
